--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_70_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_70_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7978</v>
+        <v>4.2218</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0095</v>
+        <v>4.6687</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2117</v>
+        <v>-0.4469</v>
       </c>
       <c r="G2" t="n">
         <v>1.7069</v>
@@ -610,13 +610,13 @@
         <v>0.232</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3382</v>
+        <v>1.7623</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4732</v>
+        <v>1.1325</v>
       </c>
       <c r="U2" t="n">
-        <v>0.865</v>
+        <v>0.6297</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4275</v>
+        <v>4.2097</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4171</v>
+        <v>5.2628</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0104</v>
+        <v>-1.0531</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8556</v>
+        <v>2.4372</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0467</v>
+        <v>4.05</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1911</v>
+        <v>-1.6128</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8464</v>
+        <v>5.2827</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7728</v>
+        <v>5.8383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0736</v>
+        <v>-0.5556</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9908</v>
+        <v>-2.8455</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7261</v>
+        <v>-1.7883</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2647</v>
+        <v>-1.0572</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9946</v>
+        <v>0.8806</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1221</v>
+        <v>0.248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1134</v>
+        <v>1.3558</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6083</v>
+        <v>1.3558</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8643</v>
+        <v>3.9302</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0519</v>
+        <v>3.2559</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1875</v>
+        <v>0.6743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4372</v>
+        <v>0.8556</v>
       </c>
       <c r="H4" t="n">
-        <v>4.05</v>
+        <v>2.0467</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6128</v>
+        <v>-1.1911</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2827</v>
+        <v>2.8464</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8383</v>
+        <v>2.7728</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5556</v>
+        <v>0.0736</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8455</v>
+        <v>-1.9908</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7883</v>
+        <v>-0.7261</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0572</v>
+        <v>-1.2647</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4648</v>
+        <v>0.4973</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.963</v>
+        <v>-0.0391</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4982</v>
+        <v>0.5364</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3558</v>
+        <v>2.1134</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3558</v>
+        <v>1.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.5051</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2987</v>
+        <v>2.022</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3021</v>
+        <v>2.3951</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0034</v>
+        <v>-0.3731</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3482</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1621</v>
+        <v>0.8854</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.963</v>
+        <v>0.13</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1251</v>
+        <v>0.7554</v>
       </c>
       <c r="V5" t="n">
         <v>4.0363</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6072</v>
+        <v>0.5178</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1715</v>
+        <v>0.4726</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4357</v>
+        <v>0.0452</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3226</v>
+        <v>0.3438</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5305</v>
+        <v>-0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2079</v>
+        <v>0.5119</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7765</v>
+        <v>0.3546</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5629</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7863</v>
+        <v>0.3546</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4539</v>
+        <v>-0.0108</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0323</v>
+        <v>-0.168</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4216</v>
+        <v>0.1573</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6067</v>
+        <v>0.174</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4129</v>
+        <v>0.118</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1937</v>
+        <v>0.056</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3662</v>
+        <v>0.2197</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3546</v>
+        <v>-0.1824</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0116</v>
+        <v>0.4021</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3438</v>
+        <v>0.3226</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.168</v>
+        <v>1.5305</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5119</v>
+        <v>-1.2079</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3546</v>
+        <v>0.7765</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.5629</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3546</v>
+        <v>-0.7863</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0108</v>
+        <v>-0.4539</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.168</v>
+        <v>-0.0323</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>-0.4216</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0224</v>
+        <v>0.2192</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.0591</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0224</v>
+        <v>0.1601</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.008</v>
+        <v>-1.6713</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7707</v>
+        <v>-1.5348</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2373</v>
+        <v>-0.1365</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3075</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3062</v>
+        <v>0.0305</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V8" t="n">
         <v>0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.02</v>
+        <v>-2.5825</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1479</v>
+        <v>-0.912</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8722</v>
+        <v>-1.6705</v>
       </c>
       <c r="G9" t="n">
         <v>0.2323</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.644</v>
+        <v>-0.2065</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4142</v>
+        <v>-3.642</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.944</v>
+        <v>-1.8693</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4702</v>
+        <v>-1.7726</v>
       </c>
       <c r="G10" t="n">
         <v>-4.8951</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>1.017</v>
+        <v>0.7892</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1221</v>
+        <v>0.1968</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8949</v>
+        <v>0.5924</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.336</v>
+        <v>-5.1036</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2462</v>
+        <v>-3.4506</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0899</v>
+        <v>-1.653</v>
       </c>
       <c r="G11" t="n">
         <v>-5.386</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.496</v>
+        <v>0.7284</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6018</v>
+        <v>0.3973</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1059</v>
+        <v>0.331</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6778999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7638</v>
+        <v>-6.5554</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8693</v>
+        <v>-4.0305</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8945</v>
+        <v>-2.5249</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7356</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9897</v>
+        <v>1.1982</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6844</v>
+        <v>0.5232</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3053</v>
+        <v>0.675</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9304</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1803</v>
+        <v>-4.433599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.328599999999999</v>
+        <v>4.0755</v>
       </c>
       <c r="F13" t="n">
         <v>-8.509</v>
@@ -1441,7 +1441,7 @@
         <v>-14.187</v>
       </c>
       <c r="J13" t="n">
-        <v>4.722900000000001</v>
+        <v>4.722899999999999</v>
       </c>
       <c r="K13" t="n">
         <v>11.5163</v>
@@ -1468,13 +1468,13 @@
         <v>9.2783</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2117</v>
+        <v>6.9586</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9677</v>
+        <v>2.7148</v>
       </c>
       <c r="U13" t="n">
-        <v>4.2438</v>
+        <v>4.2436</v>
       </c>
       <c r="V13" t="n">
         <v>6.180799999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8173</v>
+        <v>8.1426</v>
       </c>
       <c r="E14" t="n">
         <v>9.212300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.395</v>
+        <v>-1.0697</v>
       </c>
       <c r="G14" t="n">
         <v>7.8418</v>
@@ -1546,13 +1546,13 @@
         <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2718</v>
+        <v>-0.9465</v>
       </c>
       <c r="T14" t="n">
         <v>-0.7073</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5645</v>
+        <v>-0.2392</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9659</v>
+        <v>5.2189</v>
       </c>
       <c r="E15" t="n">
-        <v>3.972</v>
+        <v>4.3258</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9939</v>
+        <v>0.8931</v>
       </c>
       <c r="G15" t="n">
         <v>6.843</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4159</v>
+        <v>-1.1628</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4189</v>
+        <v>-1.0651</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0031</v>
+        <v>-0.0977</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.342</v>
+        <v>2.7967</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2503</v>
+        <v>1.6042</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0917</v>
+        <v>1.1925</v>
       </c>
       <c r="G16" t="n">
         <v>1.6695</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.415</v>
+        <v>-0.9603</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2948</v>
+        <v>-0.1939</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7894</v>
+        <v>0.492</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001</v>
+        <v>-0.3529</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7885</v>
+        <v>0.8449</v>
       </c>
       <c r="G17" t="n">
         <v>0.3748</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2992</v>
+        <v>-0.5966</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0351</v>
+        <v>-0.389</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.264</v>
+        <v>-0.2076</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6778999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7716</v>
+        <v>-0.2544</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0185</v>
+        <v>-0.3723</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7901</v>
+        <v>0.1179</v>
       </c>
       <c r="G18" t="n">
         <v>0.2597</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4244</v>
+        <v>-0.6016</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1845</v>
+        <v>-0.5384</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6089</v>
+        <v>-0.0633</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7968</v>
+        <v>-0.5223</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0459</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8688</v>
+        <v>-0.4763</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5212</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4327</v>
+        <v>-0.1582</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4722</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4665</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7264</v>
+        <v>-0.4904</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1683</v>
+        <v>-0.0675</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5085</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6207</v>
+        <v>-0.284</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2473</v>
+        <v>-0.1465</v>
       </c>
       <c r="V20" t="n">
         <v>0.9304</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9089</v>
+        <v>-0.791</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1326</v>
+        <v>-0.0146</v>
       </c>
       <c r="F21" t="n">
         <v>-0.7763</v>
@@ -2092,10 +2092,10 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3066</v>
+        <v>-0.1887</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U21" t="n">
         <v>-0.1573</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2513</v>
+        <v>-2.4643</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8939</v>
+        <v>-1.1299</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3573</v>
+        <v>-1.3345</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0715</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1423</v>
+        <v>-0.0707</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0395</v>
+        <v>-0.1964</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1028</v>
+        <v>0.1256</v>
       </c>
       <c r="V22" t="n">
         <v>0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6542</v>
+        <v>-6.0937</v>
       </c>
       <c r="E23" t="n">
         <v>-3.5494</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1048</v>
+        <v>-2.5443</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1196</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0165</v>
+        <v>-0.456</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3339</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6827</v>
+        <v>-0.1221</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8223</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.180299999999998</v>
+        <v>5.966499999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>9.1868</v>
+        <v>9.186900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.0063</v>
+        <v>-3.2202</v>
       </c>
       <c r="G24" t="n">
         <v>11.774</v>
@@ -2326,13 +2326,13 @@
         <v>15.077</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.2117</v>
+        <v>-5.425400000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.2437</v>
+        <v>-4.2438</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.968</v>
+        <v>-1.1817</v>
       </c>
       <c r="V24" t="n">
         <v>-6.1807</v>
